--- a/public/docs/ImportRuanganTemplate.xlsx
+++ b/public/docs/ImportRuanganTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahwal\Documents\Template Exel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fauza\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0AA4D0-E2AA-41C2-BC35-E9071675FE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B28950B-80DF-465C-8C66-E67AA082FE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="3990" windowWidth="20400" windowHeight="11835" xr2:uid="{8357153D-69A2-40FD-862B-8A2D6B1FD973}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8357153D-69A2-40FD-862B-8A2D6B1FD973}"/>
   </bookViews>
   <sheets>
     <sheet name="Import Ruangan" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>ICU-01</t>
   </si>
@@ -61,9 +61,6 @@
     <t>catatan</t>
   </si>
   <si>
-    <t>Jl.Rumah Sakit Empang</t>
-  </si>
-  <si>
     <t>Nama Ruangan</t>
   </si>
   <si>
@@ -95,6 +92,12 @@
   </si>
   <si>
     <t>NOTE :BUKA BATAS PENGISIAN</t>
+  </si>
+  <si>
+    <t>Lantai 3</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -105,30 +108,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -147,6 +126,28 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -213,39 +214,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,44 +562,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7B94FD-A24B-42C1-ABE6-EA2FADB10EC8}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>19</v>
+      <c r="F2" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -612,93 +612,94 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="36.28515625" customWidth="1"/>
-    <col min="4" max="4" width="60.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" customWidth="1"/>
+    <col min="4" max="4" width="60.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="11">
+        <v>100</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1">
-        <v>100</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="11">
+        <v>50</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="11">
         <v>10</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F10" s="5"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F9" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
